--- a/config/bracket_config.xlsx
+++ b/config/bracket_config.xlsx
@@ -10,6 +10,7 @@
     <sheet name="AgeEligibility" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Options" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="WeightClasses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GenerationMethods" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2454,4 +2455,154 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MethodKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>DisplayLabel</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ButtonLabel</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MinFighters</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>MaxFighters</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Special Cases</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pools</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pools (≤5 fighters)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pools</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Double Pools (6-10)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KO Brackets (11+)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="n">
+        <v>999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/config/bracket_config.xlsx
+++ b/config/bracket_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="AgeEligibility"/>
@@ -232,7 +232,7 @@
     <t>U11_pool_size</t>
   </si>
   <si>
-    <t>4</t>
+    <t>max_age</t>
   </si>
   <si>
     <t>BirthYear</t>
@@ -252,19 +252,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -308,14 +302,14 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -622,16 +616,16 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="2" t="s">
         <v>72</v>
       </c>
@@ -654,8 +648,8 @@
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="2">
         <v>2020</v>
       </c>
       <c r="B2" s="1"/>
@@ -665,8 +659,8 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="2">
         <v>2019</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -678,8 +672,8 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="2">
         <v>2018</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -691,8 +685,8 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="2">
         <v>2017</v>
       </c>
       <c r="B5" s="1"/>
@@ -704,8 +698,8 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="2">
         <v>2016</v>
       </c>
       <c r="B6" s="1"/>
@@ -717,8 +711,8 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="2">
         <v>2015</v>
       </c>
       <c r="B7" s="1"/>
@@ -730,8 +724,8 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="2">
         <v>2014</v>
       </c>
       <c r="B8" s="1"/>
@@ -745,8 +739,8 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="2">
         <v>2013</v>
       </c>
       <c r="B9" s="1"/>
@@ -758,8 +752,8 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="2">
         <v>2012</v>
       </c>
       <c r="B10" s="1"/>
@@ -773,8 +767,8 @@
       </c>
       <c r="G10" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="2">
         <v>2011</v>
       </c>
       <c r="B11" s="1"/>
@@ -786,8 +780,8 @@
       </c>
       <c r="G11" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="2">
         <v>2010</v>
       </c>
       <c r="B12" s="1"/>
@@ -799,8 +793,8 @@
       </c>
       <c r="G12" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="2">
         <v>2009</v>
       </c>
       <c r="B13" s="1"/>
@@ -815,7 +809,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>2008</v>
       </c>
       <c r="B14" s="1"/>
@@ -828,7 +822,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>2007</v>
       </c>
       <c r="B15" s="1"/>
@@ -841,7 +835,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>2006</v>
       </c>
       <c r="B16" s="1"/>
@@ -854,7 +848,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>2005</v>
       </c>
       <c r="B17" s="1"/>
@@ -876,11 +870,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -919,8 +913,16 @@
       <c r="A5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>71</v>
+      </c>
+      <c r="B6" s="5">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -936,11 +938,11 @@
   <dimension ref="A1:E72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -967,10 +969,10 @@
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>0</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>28</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -984,10 +986,10 @@
       <c r="B3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>28</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1001,10 +1003,10 @@
       <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>31</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -1018,10 +1020,10 @@
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>34</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -1035,10 +1037,10 @@
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>37</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1052,10 +1054,10 @@
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>40</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1069,10 +1071,10 @@
       <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>43</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1086,10 +1088,10 @@
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>46</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1103,10 +1105,10 @@
       <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>50</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1120,10 +1122,10 @@
       <c r="B11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>55</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>999</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1137,10 +1139,10 @@
       <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>0</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>34</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1154,10 +1156,10 @@
       <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>34</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>37</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1171,10 +1173,10 @@
       <c r="B14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>37</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>40</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1188,10 +1190,10 @@
       <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>40</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <v>43</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1205,10 +1207,10 @@
       <c r="B16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>43</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>46</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1222,10 +1224,10 @@
       <c r="B17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>46</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>50</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1239,10 +1241,10 @@
       <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>50</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>55</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -1256,10 +1258,10 @@
       <c r="B19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>55</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>60</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -1273,10 +1275,10 @@
       <c r="B20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <v>60</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <v>66</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1290,10 +1292,10 @@
       <c r="B21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <v>66</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <v>999</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1307,10 +1309,10 @@
       <c r="B22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <v>0</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="2">
         <v>46</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1324,10 +1326,10 @@
       <c r="B23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="2">
         <v>46</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="2">
         <v>50</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -1341,10 +1343,10 @@
       <c r="B24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="2">
         <v>50</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="2">
         <v>55</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -1358,10 +1360,10 @@
       <c r="B25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="2">
         <v>55</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="2">
         <v>60</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -1375,10 +1377,10 @@
       <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="2">
         <v>60</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="2">
         <v>66</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -1392,10 +1394,10 @@
       <c r="B27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="2">
         <v>66</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="2">
         <v>73</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -1409,10 +1411,10 @@
       <c r="B28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="2">
         <v>73</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="2">
         <v>81</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -1426,10 +1428,10 @@
       <c r="B29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="2">
         <v>81</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="2">
         <v>90</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -1443,10 +1445,10 @@
       <c r="B30" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="2">
         <v>90</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="2">
         <v>999</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -1460,10 +1462,10 @@
       <c r="B31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="2">
         <v>0</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="2">
         <v>60</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -1477,10 +1479,10 @@
       <c r="B32" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="2">
         <v>60</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="2">
         <v>66</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -1494,10 +1496,10 @@
       <c r="B33" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="2">
         <v>66</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="2">
         <v>73</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -1511,10 +1513,10 @@
       <c r="B34" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="2">
         <v>73</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="2">
         <v>81</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -1528,10 +1530,10 @@
       <c r="B35" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="2">
         <v>81</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="2">
         <v>90</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -1545,10 +1547,10 @@
       <c r="B36" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="2">
         <v>90</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="2">
         <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -1562,10 +1564,10 @@
       <c r="B37" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="2">
         <v>100</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="2">
         <v>999</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -1579,10 +1581,10 @@
       <c r="B38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="2">
         <v>0</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="2">
         <v>27</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -1596,10 +1598,10 @@
       <c r="B39" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="2">
         <v>27</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="2">
         <v>30</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -1613,10 +1615,10 @@
       <c r="B40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="2">
         <v>30</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="2">
         <v>33</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -1630,10 +1632,10 @@
       <c r="B41" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="2">
         <v>33</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="2">
         <v>36</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -1647,10 +1649,10 @@
       <c r="B42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="2">
         <v>36</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="2">
         <v>40</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -1664,10 +1666,10 @@
       <c r="B43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="2">
         <v>40</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="2">
         <v>44</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -1681,10 +1683,10 @@
       <c r="B44" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="2">
         <v>44</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="2">
         <v>48</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -1698,10 +1700,10 @@
       <c r="B45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="2">
         <v>48</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="2">
         <v>52</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -1715,10 +1717,10 @@
       <c r="B46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="2">
         <v>52</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="2">
         <v>57</v>
       </c>
       <c r="E46" s="1" t="s">
@@ -1732,10 +1734,10 @@
       <c r="B47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="2">
         <v>57</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="2">
         <v>999</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -1749,10 +1751,10 @@
       <c r="B48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="2">
         <v>0</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="2">
         <v>33</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -1766,10 +1768,10 @@
       <c r="B49" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="2">
         <v>33</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="2">
         <v>36</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -1783,10 +1785,10 @@
       <c r="B50" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="2">
         <v>36</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="2">
         <v>40</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -1800,10 +1802,10 @@
       <c r="B51" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="2">
         <v>40</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="2">
         <v>44</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -1817,10 +1819,10 @@
       <c r="B52" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="2">
         <v>44</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="2">
         <v>48</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -1834,10 +1836,10 @@
       <c r="B53" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="2">
         <v>48</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="2">
         <v>52</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -1851,10 +1853,10 @@
       <c r="B54" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="2">
         <v>52</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="2">
         <v>57</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -1868,10 +1870,10 @@
       <c r="B55" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="2">
         <v>57</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="2">
         <v>63</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -1885,10 +1887,10 @@
       <c r="B56" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="2">
         <v>63</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="2">
         <v>999</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -1902,10 +1904,10 @@
       <c r="B57" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="2">
         <v>0</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="2">
         <v>40</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -1919,10 +1921,10 @@
       <c r="B58" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="2">
         <v>40</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="2">
         <v>44</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -1936,10 +1938,10 @@
       <c r="B59" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="2">
         <v>44</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="2">
         <v>48</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -1953,10 +1955,10 @@
       <c r="B60" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="2">
         <v>48</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="2">
         <v>52</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -1970,10 +1972,10 @@
       <c r="B61" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="2">
         <v>52</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="2">
         <v>57</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -1987,10 +1989,10 @@
       <c r="B62" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="2">
         <v>57</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="2">
         <v>63</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -2004,10 +2006,10 @@
       <c r="B63" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="2">
         <v>63</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63" s="2">
         <v>70</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -2021,10 +2023,10 @@
       <c r="B64" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="2">
         <v>70</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="2">
         <v>78</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -2038,10 +2040,10 @@
       <c r="B65" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="2">
         <v>78</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65" s="2">
         <v>999</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -2055,10 +2057,10 @@
       <c r="B66" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="2">
         <v>0</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="2">
         <v>48</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -2072,10 +2074,10 @@
       <c r="B67" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="2">
         <v>48</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="2">
         <v>52</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -2089,10 +2091,10 @@
       <c r="B68" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="2">
         <v>52</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="2">
         <v>57</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -2106,10 +2108,10 @@
       <c r="B69" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="2">
         <v>57</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69" s="2">
         <v>63</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -2123,10 +2125,10 @@
       <c r="B70" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="2">
         <v>63</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="2">
         <v>70</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -2140,10 +2142,10 @@
       <c r="B71" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="2">
         <v>70</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71" s="2">
         <v>78</v>
       </c>
       <c r="E71" s="1" t="s">
@@ -2157,10 +2159,10 @@
       <c r="B72" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="2">
         <v>78</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="2">
         <v>999</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -2180,12 +2182,12 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -2218,13 +2220,13 @@
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>3</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>4</v>
       </c>
     </row>
@@ -2238,13 +2240,13 @@
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>3</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>6</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2258,13 +2260,13 @@
       <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>6</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>11</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>2</v>
       </c>
     </row>
@@ -2278,13 +2280,13 @@
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>11</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>999</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>3</v>
       </c>
     </row>
